--- a/artfynd/A 58737-2022 artfynd.xlsx
+++ b/artfynd/A 58737-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58737-2022 artfynd.xlsx
+++ b/artfynd/A 58737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>1866827</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545856.2908660186</v>
+        <v>545856</v>
       </c>
       <c r="R2" t="n">
-        <v>7036323.750465791</v>
+        <v>7036324</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2071213</v>
+        <v>1992916</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545955.5986704847</v>
+        <v>545943</v>
       </c>
       <c r="R3" t="n">
-        <v>7036303.254321414</v>
+        <v>7036403</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6633322</v>
+        <v>2071213</v>
       </c>
       <c r="B4" t="n">
-        <v>92501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1004672</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545864.3921414902</v>
+        <v>545956</v>
       </c>
       <c r="R4" t="n">
-        <v>7036321.182283573</v>
+        <v>7036303</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2012-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +971,208 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5931363</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Middagsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545798</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036390</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6633322</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Middagsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545864</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036321</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 58737-2022 artfynd.xlsx
+++ b/artfynd/A 58737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1866827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1992916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2071213</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5931363</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6633322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>